--- a/خطة_الاعتماد_المختصرة.xlsx
+++ b/خطة_الاعتماد_المختصرة.xlsx
@@ -12,12 +12,13 @@
     <sheet name="الملخص" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="الأهلية والنماذج" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="خارطة المراحل" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="فحص-البرنامج1" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="فحص-البرنامج2" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="مراجعة الرسالة" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="فحص-البرنامج1" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="فحص-البرنامج2" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'فحص-البرنامج1'!$A$3:$L$207</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'فحص-البرنامج2'!$A$3:$L$207</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'فحص-البرنامج1'!$A$3:$L$207</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'فحص-البرنامج2'!$A$3:$L$207</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="604">
   <si>
     <t xml:space="preserve">خطة المرحلة الأولى للاعتماد البرامجي: التحقق من الأدلة وتحديد الفجوات</t>
   </si>
@@ -70,7 +71,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">اجتماع الانطلاق وورشة لنشر ثقافة الاعتماد لمنسوبي القسمين، والتحقق من شروط الأهلية (الترخيص + دفعة متخرجة) ومن توفر النماذج المعتمدة TP-150 إلى TP-156 (ورقة "الأهلية والنماذج")، وإنشاء مستودع الأدلة وترميزه، وتقييم 3 أدلة معاً لتوحيد الحكم</t>
+    <t xml:space="preserve">اجتماع الانطلاق، والتحقق من شروط الأهلية (الترخيص + دفعة متخرجة) ومن توفر النماذج المعتمدة TP-150 إلى TP-156 (ورقة "الأهلية والنماذج")، وإنشاء مستودع الأدلة وترميزه، وتقييم 3 أدلة معاً لتوحيد الحكم</t>
   </si>
   <si>
     <t xml:space="preserve">رئيس اللجنة + المنسق</t>
@@ -82,7 +83,7 @@
     <t xml:space="preserve">2 – 3</t>
   </si>
   <si>
-    <t xml:space="preserve">جمع الأدلة للبرنامجين معاً وتعبئة "حالة الدليل" و"سبب النقص"، مع مراجعة نواتج التعلم ومصفوفات المقررات وأساليب التقييم، وإشراك أعضاء هيئة التدريس، ومخاطبة الجهات المساندة</t>
+    <t xml:space="preserve">مراجعة رسالة البرنامجين وأهدافهما (ورقة "مراجعة الرسالة")، وجمع الأدلة للبرنامجين معاً وتعبئة "حالة الدليل" و"سبب النقص"، مع مراجعة نواتج التعلم ومصفوفات المقررات وأساليب التقييم، وإشراك أعضاء هيئة التدريس، ومخاطبة الجهات المساندة</t>
   </si>
   <si>
     <t xml:space="preserve">كل عضو في معاييره</t>
@@ -115,7 +116,7 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">تقرير الجاهزية (من ورقة الملخص) مع الميزانية التقديرية، وعرضه على مجلس القسم/الكلية لاعتماد خطة المعالجة والانتقال إلى المرحلة التالية (ورقة "خارطة المراحل")</t>
+    <t xml:space="preserve">تقرير الجاهزية (من ورقة الملخص) وعرضه على مجلس القسم/الكلية لاعتماد خطة المعالجة والانتقال إلى المرحلة التالية (ورقة "خارطة المراحل")</t>
   </si>
   <si>
     <t xml:space="preserve">تقرير جاهزية معتمد</t>
@@ -526,7 +527,10 @@
     <t xml:space="preserve">موارد مخصصة لمتطلبات العملية</t>
   </si>
   <si>
-    <t xml:space="preserve">الأسبوع 6 (مع التقرير)</t>
+    <t xml:space="preserve">مؤجلة بقرار اللجنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
   </si>
   <si>
     <t xml:space="preserve">مراجعة الرسالة والأهداف</t>
@@ -535,7 +539,7 @@
     <t xml:space="preserve">محور العملية وما يميز البرنامج</t>
   </si>
   <si>
-    <t xml:space="preserve">الأسابيع 2 – 3 (معيار 1-1-1)</t>
+    <t xml:space="preserve">الأسابيع 2 – 3 (ورقة مراجعة الرسالة)</t>
   </si>
   <si>
     <t xml:space="preserve">فريق المجال 1</t>
@@ -547,81 +551,84 @@
     <t xml:space="preserve">لا يستطيع الفريق إنجاز المهمة منفرداً</t>
   </si>
   <si>
+    <t xml:space="preserve">مدمجة: استطلاع الرسالة (أ2–3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نشر ثقافة الاعتماد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المفاهيم والمعايير والمراحل وأثرها في الخريج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مؤجلة – تُنفّذ قبل الزيارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المرحلة 2: مراجعة البرنامج الأكاديمي وتقويمه – المخرج: برنامج مراجَع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مراجعة نواتج تعلم البرنامج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شمولها وحداثتها واتساقها مع الإطار الوطني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسابيع 2 – 3 (المجال 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فريق نواتج التعلم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مراجعة نواتج تعلم المقررات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التأكد من أن المقررات تحقق نواتج البرنامج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسابيع 2 – 3 (معيار 4-2-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مراجعة أساليب التقييم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تقييم قائم على الأداء وتوظيف المعرفة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسابيع 2 – 3 (محور 2-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إعداد وثائق التطوير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أوراق توجيهية تبيّن موقف البرنامج من التطوير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسبوع 5 (خطة الاستكمال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جميع الأعضاء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بناء نظام التقويم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آلية منتظمة لجمع الأدلة على الالتزام بالمعايير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرحلة لاحقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المنسق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جمع الأدلة وفق المعايير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بيانات الطلاب والخريجين على مدى الدراسة</t>
+  </si>
+  <si>
     <t xml:space="preserve">الأسابيع 2 – 3</t>
   </si>
   <si>
-    <t xml:space="preserve">جميع الأعضاء</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نشر ثقافة الاعتماد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المفاهيم والمعايير والمراحل وأثرها في الخريج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأسبوع 1 ومستمر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المرحلة 2: مراجعة البرنامج الأكاديمي وتقويمه – المخرج: برنامج مراجَع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مراجعة نواتج تعلم البرنامج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شمولها وحداثتها واتساقها مع الإطار الوطني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأسابيع 2 – 3 (المجال 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فريق نواتج التعلم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مراجعة نواتج تعلم المقررات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التأكد من أن المقررات تحقق نواتج البرنامج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأسابيع 2 – 3 (معيار 4-2-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مراجعة أساليب التقييم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تقييم قائم على الأداء وتوظيف المعرفة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأسابيع 2 – 3 (محور 2-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إعداد وثائق التطوير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أوراق توجيهية تبيّن موقف البرنامج من التطوير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأسبوع 5 (خطة الاستكمال)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بناء نظام التقويم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آلية منتظمة لجمع الأدلة على الالتزام بالمعايير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مرحلة لاحقة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المنسق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جمع الأدلة وفق المعايير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بيانات الطلاب والخريجين على مدى الدراسة</t>
-  </si>
-  <si>
     <t xml:space="preserve">تقديم طلب الاعتماد (TP-100)</t>
   </si>
   <si>
@@ -749,6 +756,171 @@
   </si>
   <si>
     <t xml:space="preserve">الخلايا الزرقاء = ضمن خطة الأسابيع الستة الحالية  •  الرمادية = مراحل لاحقة تُخطط بعد اعتماد تقرير الجاهزية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مراجعة رسالة البرنامج وأهدافه (المعيار 1-1-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف: التأكد من أن الرسالة والأهداف متسقة مع رسالة الجامعة والكلية، وواضحة وقابلة للقياس، وأنها فعلاً توجّه نواتج التعلم والمنهج والخطة التشغيلية. المسؤول: فريق المجال 1 (العضوان 3 و4) – الأسبوعان 2 و3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① خطوات المراجعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ماذا نفعل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المخرج (الدليل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جمع الوثائق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رسالة الجامعة والكلية وأهدافهما، ورسالة البرنامج وأهدافه الحالية، وتوصيف البرنامج TP-151، والخطة التشغيلية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملف الوثائق في المستودع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفحص بقائمة التحقق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يطبق الفريق قائمة التحقق ② على الرسالة والأهداف الحالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قائمة تحقق معبأة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصفوفة الاتساق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ربط كل هدف من أهداف البرنامج بأهداف الكلية والجامعة (النموذج ③)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استطلاع رأي مختصر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأسئلة ④ لأعضاء هيئة التدريس والطلاب والخريجين وجهات التوظيف (نموذج إلكتروني، أسبوع واحد)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تقرير نتائج الاستطلاع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القرار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إبقاء كما هي / تعديل صياغة طفيف / إعادة صياغة. يُفضّل التعديل الطفيف لأن تغيير الرسالة جذرياً ينعكس على النواتج والتوصيفات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">توصية اللجنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الاعتماد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رفع الصيغة إلى مجلس القسم ثم مجلس الكلية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محضر اعتماد المجلس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">النشر والتحديث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الموقع الإلكتروني، دليل الطالب، توصيف البرنامج، اللوحات داخل القسم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">روابط وصور النشر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">② قائمة التحقق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السؤال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل الرسالة مختصرة وواضحة (سطران إلى ثلاثة) ويسهل تذكرها؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل تبيّن الرسالة ما يميز البرنامج عن البرامج المماثلة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل الرسالة متسقة مع رسالة الكلية والجامعة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل تغطي الأهداف مجالات التعليم والبحث العلمي وخدمة المجتمع؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل الأهداف محددة وقابلة للقياس، ولكل هدف مؤشر أداء؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل ترتبط الأهداف بنواتج التعلم وخصائص الخريجين؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل تراعي الأهداف احتياجات سوق العمل؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل الرسالة والأهداف معتمدة من المجالس ومنشورة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل الخطة التشغيلية للبرنامج مبنية على هذه الأهداف؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عدد "نعم"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">③ نموذج مصفوفة الاتساق (يُعبأ لكل برنامج – ضع ✓ عند وجود ارتباط)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هدف البرنامج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هدف الكلية ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هدف الجامعة ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف 1: ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف 2: ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف 3: ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف 4: ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الهدف 5: ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كل هدف من أهداف البرنامج يجب أن يرتبط بهدف واحد على الأقل من أهداف الكلية أو الجامعة؛ الهدف الذي لا يرتبط بشيء يُعاد النظر فيه.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ أسئلة الاستطلاع المختصر (مقياس: موافق بشدة ← غير موافق بشدة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أعرف رسالة البرنامج وأهدافه.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرسالة والأهداف واضحة ومفهومة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الرسالة تعبّر عما يميز البرنامج.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أنشطة البرنامج ومقرراته تحقق رسالته وأهدافه.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأهداف تلبي احتياجات سوق العمل.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سؤال مفتوح: ما مقترحك لتحسين صياغة الرسالة أو الأهداف؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يغطي هذا الاستطلاع دليل "تقرير استطلاع رأي المستفيدين حول وضوح ونشر الرسالة والأهداف" في المعيار 1-1-1، ويُعد في الوقت نفسه إشراكاً للمنتسبين.</t>
   </si>
   <si>
     <t xml:space="preserve">عبّئ الخلايا الصفراء فقط: اختر حالة الدليل، وإن كان ناقصاً اختر السبب واكتب الإجراء والموعد. الصفوف المظللة = معايير أساسية ★</t>
@@ -2243,7 +2415,7 @@
       <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF548235"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
@@ -3615,7 +3787,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CE39EA54-A939-40F5-B5E3-99D9DE508142}</x14:id>
+          <x14:id>{9DBA00CD-BE26-4EFF-ADB9-69CD89F52078}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3629,7 +3801,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{499F5297-83F2-4232-A61F-549F21C77528}</x14:id>
+          <x14:id>{DD511ECF-2333-4915-BB6E-51244E71B563}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3645,7 +3817,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CE39EA54-A939-40F5-B5E3-99D9DE508142}">
+          <x14:cfRule type="dataBar" id="{9DBA00CD-BE26-4EFF-ADB9-69CD89F52078}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3660,7 +3832,7 @@
           <xm:sqref>G6:G12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{499F5297-83F2-4232-A61F-549F21C77528}">
+          <x14:cfRule type="dataBar" id="{DD511ECF-2333-4915-BB6E-51244E71B563}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -4252,11 +4424,11 @@
       <c r="C10" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="25" t="s">
         <v>165</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>153</v>
@@ -4267,16 +4439,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>153</v>
@@ -4287,16 +4459,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>170</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>153</v>
@@ -4312,7 +4484,7 @@
       <c r="C13" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="25" t="s">
         <v>176</v>
       </c>
       <c r="E13" s="9" t="s">
@@ -4406,7 +4578,7 @@
         <v>190</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>153</v>
@@ -4417,16 +4589,16 @@
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>153</v>
@@ -4437,16 +4609,16 @@
         <v>6</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>153</v>
@@ -4457,13 +4629,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>38</v>
@@ -4477,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>153</v>
@@ -4494,7 +4666,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -4507,16 +4679,16 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>152</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>153</v>
@@ -4530,13 +4702,13 @@
         <v>26</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>153</v>
@@ -4547,16 +4719,16 @@
         <v>3</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D26" s="24" t="s">
         <v>152</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>153</v>
@@ -4567,16 +4739,16 @@
         <v>4</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>153</v>
@@ -4587,13 +4759,13 @@
         <v>5</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>38</v>
@@ -4607,13 +4779,13 @@
         <v>6</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>38</v>
@@ -4627,13 +4799,13 @@
         <v>7</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>38</v>
@@ -4647,13 +4819,13 @@
         <v>8</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>38</v>
@@ -4664,7 +4836,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -4677,16 +4849,16 @@
         <v>1</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>153</v>
@@ -4697,16 +4869,16 @@
         <v>2</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>153</v>
@@ -4717,13 +4889,13 @@
         <v>3</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>38</v>
@@ -4737,16 +4909,16 @@
         <v>4</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>153</v>
@@ -4757,13 +4929,13 @@
         <v>5</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>38</v>
@@ -4777,16 +4949,16 @@
         <v>6</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>153</v>
@@ -4797,16 +4969,16 @@
         <v>7</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>153</v>
@@ -4817,16 +4989,16 @@
         <v>8</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>153</v>
@@ -4834,7 +5006,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4876,6 +5048,612 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF548235"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="22" t="str">
+        <f aca="false">COUNTIF(E16:E24,"نعم")&amp;" من 9"</f>
+        <v>0 من 9</v>
+      </c>
+      <c r="F25" s="22" t="str">
+        <f aca="false">COUNTIF(F16:F24,"نعم")&amp;" من 9"</f>
+        <v>0 من 9</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A44:F44"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E16:F24">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"نعم"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"جزئياً"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>"لا"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:F12" type="list">
+      <formula1>"لم تبدأ,قيد التنفيذ,مكتملة"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E16:F24" type="list">
+      <formula1>"نعم,جزئياً,لا"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FF8EA9DB"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -4909,7 +5687,7 @@
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -4925,16 +5703,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>241</v>
+        <v>298</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>9</v>
@@ -4946,16 +5724,16 @@
         <v>89</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>247</v>
+        <v>304</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>99</v>
@@ -4963,14 +5741,14 @@
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>250</v>
+        <v>307</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="29" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="E4" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -4989,12 +5767,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="30"/>
       <c r="D5" s="29" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="E5" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5013,12 +5791,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B6" s="29"/>
       <c r="C6" s="30"/>
       <c r="D6" s="29" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="E6" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5037,12 +5815,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="29" t="s">
-        <v>254</v>
+        <v>311</v>
       </c>
       <c r="E7" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5061,16 +5839,16 @@
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>256</v>
+        <v>313</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="E8" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5089,14 +5867,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="E9" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5115,14 +5893,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B10" s="43"/>
       <c r="C10" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="E10" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5141,14 +5919,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B11" s="43"/>
       <c r="C11" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="E11" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5167,14 +5945,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B12" s="43"/>
       <c r="C12" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>262</v>
+        <v>319</v>
       </c>
       <c r="E12" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5193,14 +5971,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="45" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="C13" s="47"/>
       <c r="D13" s="46" t="s">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="E13" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5219,12 +5997,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="29" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="E14" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5243,12 +6021,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="29" t="s">
-        <v>267</v>
+        <v>324</v>
       </c>
       <c r="E15" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5267,12 +6045,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="29" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="E16" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5291,12 +6069,12 @@
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="29" t="s">
-        <v>269</v>
+        <v>326</v>
       </c>
       <c r="E17" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5315,14 +6093,14 @@
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="46" t="s">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="E18" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5341,12 +6119,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="29" t="s">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="E19" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5365,14 +6143,14 @@
     </row>
     <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>275</v>
+        <v>332</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="46" t="s">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5391,12 +6169,12 @@
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="29" t="s">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="E21" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5415,12 +6193,12 @@
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="29" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="E22" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5439,12 +6217,12 @@
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="29" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="E23" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5463,14 +6241,14 @@
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="45" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>281</v>
+        <v>338</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="46" t="s">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5489,12 +6267,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="29" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="E25" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5513,12 +6291,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="29" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="E26" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5537,12 +6315,12 @@
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="29" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="E27" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5561,14 +6339,14 @@
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="45" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="C28" s="47"/>
       <c r="D28" s="46" t="s">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="E28" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5587,12 +6365,12 @@
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="29" t="s">
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="E29" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5611,12 +6389,12 @@
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="29" t="s">
-        <v>290</v>
+        <v>347</v>
       </c>
       <c r="E30" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5635,12 +6413,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="29" t="s">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="E31" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5659,12 +6437,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="29" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
       <c r="E32" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5683,16 +6461,16 @@
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="35" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>295</v>
+        <v>352</v>
       </c>
       <c r="E33" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5711,14 +6489,14 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B34" s="43"/>
       <c r="C34" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>296</v>
+        <v>353</v>
       </c>
       <c r="E34" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5737,14 +6515,14 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B35" s="43"/>
       <c r="C35" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="E35" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5763,14 +6541,14 @@
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B36" s="43"/>
       <c r="C36" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="E36" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5789,14 +6567,14 @@
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B37" s="43"/>
       <c r="C37" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>299</v>
+        <v>356</v>
       </c>
       <c r="E37" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5815,14 +6593,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B38" s="43"/>
       <c r="C38" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="E38" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5841,14 +6619,14 @@
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="45" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B39" s="46" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
       <c r="C39" s="47"/>
       <c r="D39" s="46" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="E39" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5867,12 +6645,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="29" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
       <c r="E40" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5891,12 +6669,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="29" t="s">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="E41" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5915,12 +6693,12 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="29" t="s">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="E42" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5939,14 +6717,14 @@
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="45" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>308</v>
+        <v>365</v>
       </c>
       <c r="C43" s="47"/>
       <c r="D43" s="46" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
       <c r="E43" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5965,12 +6743,12 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="29" t="s">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="E44" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -5989,12 +6767,12 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="29" t="s">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="E45" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6013,12 +6791,12 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="29" t="s">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="E46" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6037,16 +6815,16 @@
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="35" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="B47" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="C47" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="C47" s="37" t="s">
-        <v>257</v>
-      </c>
       <c r="D47" s="36" t="s">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="E47" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6065,14 +6843,14 @@
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="42" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="B48" s="43"/>
       <c r="C48" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>316</v>
+        <v>373</v>
       </c>
       <c r="E48" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6091,14 +6869,14 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="42" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="B49" s="43"/>
       <c r="C49" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>317</v>
+        <v>374</v>
       </c>
       <c r="E49" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6117,14 +6895,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="45" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>319</v>
+        <v>376</v>
       </c>
       <c r="C50" s="47"/>
       <c r="D50" s="46" t="s">
-        <v>320</v>
+        <v>377</v>
       </c>
       <c r="E50" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6143,12 +6921,12 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="29" t="s">
-        <v>321</v>
+        <v>378</v>
       </c>
       <c r="E51" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6167,12 +6945,12 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="29" t="s">
-        <v>322</v>
+        <v>379</v>
       </c>
       <c r="E52" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6191,12 +6969,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="29" t="s">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="E53" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6215,12 +6993,12 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="29" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="E54" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6239,12 +7017,12 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="29" t="s">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="E55" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$21</f>
@@ -6263,14 +7041,14 @@
     </row>
     <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="45" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B56" s="46" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="C56" s="47"/>
       <c r="D56" s="46" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="E56" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6289,12 +7067,12 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="29" t="s">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="E57" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6313,12 +7091,12 @@
     </row>
     <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="29" t="s">
-        <v>330</v>
+        <v>387</v>
       </c>
       <c r="E58" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6337,12 +7115,12 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="29" t="s">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="E59" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6361,12 +7139,12 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="29" t="s">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="E60" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6385,12 +7163,12 @@
     </row>
     <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="29" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="E61" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6409,12 +7187,12 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="29" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="E62" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6433,12 +7211,12 @@
     </row>
     <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="29" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="E63" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6457,12 +7235,12 @@
     </row>
     <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="29" t="s">
-        <v>336</v>
+        <v>393</v>
       </c>
       <c r="E64" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6481,12 +7259,12 @@
     </row>
     <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="29" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="E65" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6505,16 +7283,16 @@
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="35" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="E66" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6533,14 +7311,14 @@
     </row>
     <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="B67" s="43"/>
       <c r="C67" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D67" s="43" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="E67" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6559,14 +7337,14 @@
     </row>
     <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="B68" s="43"/>
       <c r="C68" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D68" s="43" t="s">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="E68" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6585,14 +7363,14 @@
     </row>
     <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="45" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B69" s="46" t="s">
-        <v>344</v>
+        <v>401</v>
       </c>
       <c r="C69" s="47"/>
       <c r="D69" s="46" t="s">
-        <v>345</v>
+        <v>402</v>
       </c>
       <c r="E69" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6611,12 +7389,12 @@
     </row>
     <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="31" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="29" t="s">
-        <v>346</v>
+        <v>403</v>
       </c>
       <c r="E70" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6635,12 +7413,12 @@
     </row>
     <row r="71" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="31" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="29" t="s">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="E71" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6659,12 +7437,12 @@
     </row>
     <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="31" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="29" t="s">
-        <v>348</v>
+        <v>405</v>
       </c>
       <c r="E72" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6683,16 +7461,16 @@
     </row>
     <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="35" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="E73" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6711,14 +7489,14 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="42" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B74" s="43"/>
       <c r="C74" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D74" s="43" t="s">
-        <v>351</v>
+        <v>408</v>
       </c>
       <c r="E74" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6737,14 +7515,14 @@
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="42" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B75" s="43"/>
       <c r="C75" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D75" s="43" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="E75" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6763,14 +7541,14 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="42" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B76" s="43"/>
       <c r="C76" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D76" s="43" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="E76" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6789,14 +7567,14 @@
     </row>
     <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="45" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="C77" s="47"/>
       <c r="D77" s="46" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="E77" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6815,12 +7593,12 @@
     </row>
     <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="31" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="29" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="E78" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6839,12 +7617,12 @@
     </row>
     <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="31" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="29" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
       <c r="E79" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6863,12 +7641,12 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="31" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="29" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="E80" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6887,16 +7665,16 @@
     </row>
     <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="35" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E81" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6915,14 +7693,14 @@
     </row>
     <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B82" s="43"/>
       <c r="C82" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D82" s="43" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="E82" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6941,14 +7719,14 @@
     </row>
     <row r="83" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B83" s="43"/>
       <c r="C83" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D83" s="43" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
       <c r="E83" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6967,14 +7745,14 @@
     </row>
     <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B84" s="43"/>
       <c r="C84" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D84" s="43" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="E84" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -6993,14 +7771,14 @@
     </row>
     <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B85" s="43"/>
       <c r="C85" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D85" s="43" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="E85" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7019,14 +7797,14 @@
     </row>
     <row r="86" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B86" s="43"/>
       <c r="C86" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D86" s="43" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="E86" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7045,16 +7823,16 @@
     </row>
     <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="35" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C87" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="E87" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7073,14 +7851,14 @@
     </row>
     <row r="88" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="42" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B88" s="43"/>
       <c r="C88" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="E88" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7099,14 +7877,14 @@
     </row>
     <row r="89" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="42" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B89" s="43"/>
       <c r="C89" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="E89" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7125,14 +7903,14 @@
     </row>
     <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="42" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B90" s="43"/>
       <c r="C90" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D90" s="43" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="E90" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7151,14 +7929,14 @@
     </row>
     <row r="91" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="45" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B91" s="46" t="s">
-        <v>374</v>
+        <v>431</v>
       </c>
       <c r="C91" s="47"/>
       <c r="D91" s="46" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="E91" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7177,12 +7955,12 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="31" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B92" s="29"/>
       <c r="C92" s="30"/>
       <c r="D92" s="29" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="E92" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7201,12 +7979,12 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="31" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B93" s="29"/>
       <c r="C93" s="30"/>
       <c r="D93" s="29" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="E93" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7225,12 +8003,12 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="31" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B94" s="29"/>
       <c r="C94" s="30"/>
       <c r="D94" s="29" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="E94" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7249,14 +8027,14 @@
     </row>
     <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="45" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B95" s="46" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C95" s="47"/>
       <c r="D95" s="46" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="E95" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7275,12 +8053,12 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="31" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B96" s="29"/>
       <c r="C96" s="30"/>
       <c r="D96" s="29" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E96" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7299,12 +8077,12 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="31" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B97" s="29"/>
       <c r="C97" s="30"/>
       <c r="D97" s="29" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="E97" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7323,12 +8101,12 @@
     </row>
     <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="31" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B98" s="29"/>
       <c r="C98" s="30"/>
       <c r="D98" s="29" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="E98" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7347,14 +8125,14 @@
     </row>
     <row r="99" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="45" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="B99" s="46" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="C99" s="47"/>
       <c r="D99" s="46" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="E99" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7373,12 +8151,12 @@
     </row>
     <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="31" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="B100" s="29"/>
       <c r="C100" s="30"/>
       <c r="D100" s="29" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="E100" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7397,14 +8175,14 @@
     </row>
     <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="45" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B101" s="46" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="C101" s="47"/>
       <c r="D101" s="46" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="E101" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7423,12 +8201,12 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="31" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B102" s="29"/>
       <c r="C102" s="30"/>
       <c r="D102" s="29" t="s">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="E102" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7447,12 +8225,12 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="31" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B103" s="29"/>
       <c r="C103" s="30"/>
       <c r="D103" s="29" t="s">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="E103" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7471,16 +8249,16 @@
     </row>
     <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="35" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>394</v>
+        <v>451</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D104" s="36" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
       <c r="E104" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7499,14 +8277,14 @@
     </row>
     <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="42" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="B105" s="43"/>
       <c r="C105" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>396</v>
+        <v>453</v>
       </c>
       <c r="E105" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$23</f>
@@ -7525,16 +8303,16 @@
     </row>
     <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="35" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="C106" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>399</v>
+        <v>456</v>
       </c>
       <c r="E106" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7553,14 +8331,14 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B107" s="43"/>
       <c r="C107" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D107" s="43" t="s">
-        <v>400</v>
+        <v>457</v>
       </c>
       <c r="E107" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7579,14 +8357,14 @@
     </row>
     <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B108" s="43"/>
       <c r="C108" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D108" s="43" t="s">
-        <v>401</v>
+        <v>458</v>
       </c>
       <c r="E108" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7605,14 +8383,14 @@
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B109" s="43"/>
       <c r="C109" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="E109" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7631,14 +8409,14 @@
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B110" s="43"/>
       <c r="C110" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D110" s="43" t="s">
-        <v>403</v>
+        <v>460</v>
       </c>
       <c r="E110" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7657,14 +8435,14 @@
     </row>
     <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="45" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B111" s="46" t="s">
-        <v>405</v>
+        <v>462</v>
       </c>
       <c r="C111" s="47"/>
       <c r="D111" s="46" t="s">
-        <v>406</v>
+        <v>463</v>
       </c>
       <c r="E111" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7683,12 +8461,12 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="31" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B112" s="29"/>
       <c r="C112" s="30"/>
       <c r="D112" s="29" t="s">
-        <v>407</v>
+        <v>464</v>
       </c>
       <c r="E112" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7707,12 +8485,12 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="31" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B113" s="29"/>
       <c r="C113" s="30"/>
       <c r="D113" s="29" t="s">
-        <v>408</v>
+        <v>465</v>
       </c>
       <c r="E113" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7731,12 +8509,12 @@
     </row>
     <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="31" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B114" s="29"/>
       <c r="C114" s="30"/>
       <c r="D114" s="29" t="s">
-        <v>409</v>
+        <v>466</v>
       </c>
       <c r="E114" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7755,14 +8533,14 @@
     </row>
     <row r="115" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="45" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="B115" s="46" t="s">
-        <v>411</v>
+        <v>468</v>
       </c>
       <c r="C115" s="47"/>
       <c r="D115" s="46" t="s">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="E115" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7781,12 +8559,12 @@
     </row>
     <row r="116" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="31" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="B116" s="29"/>
       <c r="C116" s="30"/>
       <c r="D116" s="29" t="s">
-        <v>413</v>
+        <v>470</v>
       </c>
       <c r="E116" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7805,12 +8583,12 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="31" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="B117" s="29"/>
       <c r="C117" s="30"/>
       <c r="D117" s="29" t="s">
-        <v>414</v>
+        <v>471</v>
       </c>
       <c r="E117" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7829,14 +8607,14 @@
     </row>
     <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="45" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="B118" s="46" t="s">
-        <v>416</v>
+        <v>473</v>
       </c>
       <c r="C118" s="47"/>
       <c r="D118" s="46" t="s">
-        <v>417</v>
+        <v>474</v>
       </c>
       <c r="E118" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7855,12 +8633,12 @@
     </row>
     <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="31" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="B119" s="29"/>
       <c r="C119" s="30"/>
       <c r="D119" s="29" t="s">
-        <v>418</v>
+        <v>475</v>
       </c>
       <c r="E119" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7879,12 +8657,12 @@
     </row>
     <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="31" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="B120" s="29"/>
       <c r="C120" s="30"/>
       <c r="D120" s="29" t="s">
-        <v>419</v>
+        <v>476</v>
       </c>
       <c r="E120" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7903,14 +8681,14 @@
     </row>
     <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="45" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B121" s="46" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="C121" s="47"/>
       <c r="D121" s="46" t="s">
-        <v>422</v>
+        <v>479</v>
       </c>
       <c r="E121" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7929,12 +8707,12 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B122" s="29"/>
       <c r="C122" s="30"/>
       <c r="D122" s="29" t="s">
-        <v>423</v>
+        <v>480</v>
       </c>
       <c r="E122" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7953,12 +8731,12 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B123" s="29"/>
       <c r="C123" s="30"/>
       <c r="D123" s="29" t="s">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="E123" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -7977,12 +8755,12 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B124" s="29"/>
       <c r="C124" s="30"/>
       <c r="D124" s="29" t="s">
-        <v>425</v>
+        <v>482</v>
       </c>
       <c r="E124" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -8001,12 +8779,12 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B125" s="29"/>
       <c r="C125" s="30"/>
       <c r="D125" s="29" t="s">
-        <v>426</v>
+        <v>483</v>
       </c>
       <c r="E125" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -8025,16 +8803,16 @@
     </row>
     <row r="126" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="35" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B126" s="36" t="s">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="C126" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D126" s="36" t="s">
-        <v>429</v>
+        <v>486</v>
       </c>
       <c r="E126" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -8053,14 +8831,14 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B127" s="43"/>
       <c r="C127" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D127" s="43" t="s">
-        <v>430</v>
+        <v>487</v>
       </c>
       <c r="E127" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -8079,14 +8857,14 @@
     </row>
     <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B128" s="43"/>
       <c r="C128" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D128" s="43" t="s">
-        <v>431</v>
+        <v>488</v>
       </c>
       <c r="E128" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -8105,14 +8883,14 @@
     </row>
     <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B129" s="43"/>
       <c r="C129" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D129" s="43" t="s">
-        <v>432</v>
+        <v>489</v>
       </c>
       <c r="E129" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -8131,14 +8909,14 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B130" s="43"/>
       <c r="C130" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D130" s="43" t="s">
-        <v>433</v>
+        <v>490</v>
       </c>
       <c r="E130" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -8157,14 +8935,14 @@
     </row>
     <row r="131" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="45" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B131" s="46" t="s">
-        <v>435</v>
+        <v>492</v>
       </c>
       <c r="C131" s="47"/>
       <c r="D131" s="46" t="s">
-        <v>436</v>
+        <v>493</v>
       </c>
       <c r="E131" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8183,12 +8961,12 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B132" s="29"/>
       <c r="C132" s="30"/>
       <c r="D132" s="29" t="s">
-        <v>437</v>
+        <v>494</v>
       </c>
       <c r="E132" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8207,12 +8985,12 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B133" s="29"/>
       <c r="C133" s="30"/>
       <c r="D133" s="29" t="s">
-        <v>438</v>
+        <v>495</v>
       </c>
       <c r="E133" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8231,12 +9009,12 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B134" s="29"/>
       <c r="C134" s="30"/>
       <c r="D134" s="29" t="s">
-        <v>439</v>
+        <v>496</v>
       </c>
       <c r="E134" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8255,12 +9033,12 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B135" s="29"/>
       <c r="C135" s="30"/>
       <c r="D135" s="29" t="s">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="E135" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8279,14 +9057,14 @@
     </row>
     <row r="136" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="45" t="s">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="B136" s="46" t="s">
-        <v>442</v>
+        <v>499</v>
       </c>
       <c r="C136" s="47"/>
       <c r="D136" s="46" t="s">
-        <v>443</v>
+        <v>500</v>
       </c>
       <c r="E136" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8305,12 +9083,12 @@
     </row>
     <row r="137" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="31" t="s">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="B137" s="29"/>
       <c r="C137" s="30"/>
       <c r="D137" s="29" t="s">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="E137" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8329,12 +9107,12 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="31" t="s">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="B138" s="29"/>
       <c r="C138" s="30"/>
       <c r="D138" s="29" t="s">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="E138" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8353,16 +9131,16 @@
     </row>
     <row r="139" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="35" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>447</v>
+        <v>504</v>
       </c>
       <c r="C139" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D139" s="36" t="s">
-        <v>448</v>
+        <v>505</v>
       </c>
       <c r="E139" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8381,14 +9159,14 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B140" s="43"/>
       <c r="C140" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D140" s="43" t="s">
-        <v>449</v>
+        <v>506</v>
       </c>
       <c r="E140" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8407,14 +9185,14 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B141" s="43"/>
       <c r="C141" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D141" s="43" t="s">
-        <v>450</v>
+        <v>507</v>
       </c>
       <c r="E141" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8433,14 +9211,14 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B142" s="43"/>
       <c r="C142" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D142" s="43" t="s">
-        <v>451</v>
+        <v>508</v>
       </c>
       <c r="E142" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8459,14 +9237,14 @@
     </row>
     <row r="143" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B143" s="43"/>
       <c r="C143" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D143" s="43" t="s">
-        <v>452</v>
+        <v>509</v>
       </c>
       <c r="E143" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8485,14 +9263,14 @@
     </row>
     <row r="144" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B144" s="43"/>
       <c r="C144" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D144" s="43" t="s">
-        <v>453</v>
+        <v>510</v>
       </c>
       <c r="E144" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8511,14 +9289,14 @@
     </row>
     <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B145" s="43"/>
       <c r="C145" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D145" s="43" t="s">
-        <v>454</v>
+        <v>511</v>
       </c>
       <c r="E145" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8537,14 +9315,14 @@
     </row>
     <row r="146" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="45" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B146" s="46" t="s">
-        <v>456</v>
+        <v>513</v>
       </c>
       <c r="C146" s="47"/>
       <c r="D146" s="46" t="s">
-        <v>457</v>
+        <v>514</v>
       </c>
       <c r="E146" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8563,12 +9341,12 @@
     </row>
     <row r="147" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="31" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B147" s="29"/>
       <c r="C147" s="30"/>
       <c r="D147" s="29" t="s">
-        <v>458</v>
+        <v>515</v>
       </c>
       <c r="E147" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8587,12 +9365,12 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="31" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B148" s="29"/>
       <c r="C148" s="30"/>
       <c r="D148" s="29" t="s">
-        <v>459</v>
+        <v>516</v>
       </c>
       <c r="E148" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8611,12 +9389,12 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="31" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B149" s="29"/>
       <c r="C149" s="30"/>
       <c r="D149" s="29" t="s">
-        <v>460</v>
+        <v>517</v>
       </c>
       <c r="E149" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8635,14 +9413,14 @@
     </row>
     <row r="150" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="45" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>462</v>
+        <v>519</v>
       </c>
       <c r="C150" s="47"/>
       <c r="D150" s="46" t="s">
-        <v>463</v>
+        <v>520</v>
       </c>
       <c r="E150" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8661,12 +9439,12 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="31" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B151" s="29"/>
       <c r="C151" s="30"/>
       <c r="D151" s="29" t="s">
-        <v>464</v>
+        <v>521</v>
       </c>
       <c r="E151" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8685,12 +9463,12 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="31" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B152" s="29"/>
       <c r="C152" s="30"/>
       <c r="D152" s="29" t="s">
-        <v>465</v>
+        <v>522</v>
       </c>
       <c r="E152" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8709,12 +9487,12 @@
     </row>
     <row r="153" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="31" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B153" s="29"/>
       <c r="C153" s="30"/>
       <c r="D153" s="29" t="s">
-        <v>466</v>
+        <v>523</v>
       </c>
       <c r="E153" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8733,14 +9511,14 @@
     </row>
     <row r="154" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="45" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>468</v>
+        <v>525</v>
       </c>
       <c r="C154" s="47"/>
       <c r="D154" s="46" t="s">
-        <v>469</v>
+        <v>526</v>
       </c>
       <c r="E154" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8759,12 +9537,12 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B155" s="29"/>
       <c r="C155" s="30"/>
       <c r="D155" s="29" t="s">
-        <v>470</v>
+        <v>527</v>
       </c>
       <c r="E155" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8783,12 +9561,12 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B156" s="29"/>
       <c r="C156" s="30"/>
       <c r="D156" s="29" t="s">
-        <v>471</v>
+        <v>528</v>
       </c>
       <c r="E156" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8807,12 +9585,12 @@
     </row>
     <row r="157" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B157" s="29"/>
       <c r="C157" s="30"/>
       <c r="D157" s="29" t="s">
-        <v>472</v>
+        <v>529</v>
       </c>
       <c r="E157" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8831,12 +9609,12 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B158" s="29"/>
       <c r="C158" s="30"/>
       <c r="D158" s="29" t="s">
-        <v>473</v>
+        <v>530</v>
       </c>
       <c r="E158" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8855,12 +9633,12 @@
     </row>
     <row r="159" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B159" s="29"/>
       <c r="C159" s="30"/>
       <c r="D159" s="29" t="s">
-        <v>474</v>
+        <v>531</v>
       </c>
       <c r="E159" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8879,16 +9657,16 @@
     </row>
     <row r="160" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="35" t="s">
-        <v>475</v>
+        <v>532</v>
       </c>
       <c r="B160" s="36" t="s">
-        <v>476</v>
+        <v>533</v>
       </c>
       <c r="C160" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D160" s="36" t="s">
-        <v>477</v>
+        <v>534</v>
       </c>
       <c r="E160" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8907,14 +9685,14 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="42" t="s">
-        <v>475</v>
+        <v>532</v>
       </c>
       <c r="B161" s="43"/>
       <c r="C161" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D161" s="43" t="s">
-        <v>478</v>
+        <v>535</v>
       </c>
       <c r="E161" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8933,14 +9711,14 @@
     </row>
     <row r="162" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="42" t="s">
-        <v>475</v>
+        <v>532</v>
       </c>
       <c r="B162" s="43"/>
       <c r="C162" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D162" s="43" t="s">
-        <v>479</v>
+        <v>536</v>
       </c>
       <c r="E162" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8959,16 +9737,16 @@
     </row>
     <row r="163" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="35" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B163" s="36" t="s">
-        <v>481</v>
+        <v>538</v>
       </c>
       <c r="C163" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D163" s="36" t="s">
-        <v>482</v>
+        <v>539</v>
       </c>
       <c r="E163" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -8987,14 +9765,14 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="42" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B164" s="43"/>
       <c r="C164" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D164" s="43" t="s">
-        <v>483</v>
+        <v>540</v>
       </c>
       <c r="E164" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9013,14 +9791,14 @@
     </row>
     <row r="165" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="42" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B165" s="43"/>
       <c r="C165" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D165" s="43" t="s">
-        <v>484</v>
+        <v>541</v>
       </c>
       <c r="E165" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9039,14 +9817,14 @@
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="42" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B166" s="43"/>
       <c r="C166" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D166" s="43" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="E166" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9065,14 +9843,14 @@
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="45" t="s">
-        <v>486</v>
+        <v>543</v>
       </c>
       <c r="B167" s="46" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="C167" s="47"/>
       <c r="D167" s="46" t="s">
-        <v>488</v>
+        <v>545</v>
       </c>
       <c r="E167" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9091,12 +9869,12 @@
     </row>
     <row r="168" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="31" t="s">
-        <v>486</v>
+        <v>543</v>
       </c>
       <c r="B168" s="29"/>
       <c r="C168" s="30"/>
       <c r="D168" s="29" t="s">
-        <v>489</v>
+        <v>546</v>
       </c>
       <c r="E168" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9115,14 +9893,14 @@
     </row>
     <row r="169" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="45" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B169" s="46" t="s">
-        <v>491</v>
+        <v>548</v>
       </c>
       <c r="C169" s="47"/>
       <c r="D169" s="46" t="s">
-        <v>492</v>
+        <v>549</v>
       </c>
       <c r="E169" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9141,12 +9919,12 @@
     </row>
     <row r="170" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B170" s="29"/>
       <c r="C170" s="30"/>
       <c r="D170" s="29" t="s">
-        <v>493</v>
+        <v>550</v>
       </c>
       <c r="E170" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9165,12 +9943,12 @@
     </row>
     <row r="171" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B171" s="29"/>
       <c r="C171" s="30"/>
       <c r="D171" s="29" t="s">
-        <v>494</v>
+        <v>551</v>
       </c>
       <c r="E171" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9189,12 +9967,12 @@
     </row>
     <row r="172" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B172" s="29"/>
       <c r="C172" s="30"/>
       <c r="D172" s="29" t="s">
-        <v>495</v>
+        <v>552</v>
       </c>
       <c r="E172" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9213,12 +9991,12 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B173" s="29"/>
       <c r="C173" s="30"/>
       <c r="D173" s="29" t="s">
-        <v>496</v>
+        <v>553</v>
       </c>
       <c r="E173" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9237,12 +10015,12 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B174" s="29"/>
       <c r="C174" s="30"/>
       <c r="D174" s="29" t="s">
-        <v>497</v>
+        <v>554</v>
       </c>
       <c r="E174" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9261,12 +10039,12 @@
     </row>
     <row r="175" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B175" s="29"/>
       <c r="C175" s="30"/>
       <c r="D175" s="29" t="s">
-        <v>498</v>
+        <v>555</v>
       </c>
       <c r="E175" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9285,14 +10063,14 @@
     </row>
     <row r="176" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="45" t="s">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="B176" s="46" t="s">
-        <v>500</v>
+        <v>557</v>
       </c>
       <c r="C176" s="47"/>
       <c r="D176" s="46" t="s">
-        <v>501</v>
+        <v>558</v>
       </c>
       <c r="E176" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9311,12 +10089,12 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="31" t="s">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="B177" s="29"/>
       <c r="C177" s="30"/>
       <c r="D177" s="29" t="s">
-        <v>502</v>
+        <v>559</v>
       </c>
       <c r="E177" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9335,12 +10113,12 @@
     </row>
     <row r="178" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="31" t="s">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="B178" s="29"/>
       <c r="C178" s="30"/>
       <c r="D178" s="29" t="s">
-        <v>503</v>
+        <v>560</v>
       </c>
       <c r="E178" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9359,14 +10137,14 @@
     </row>
     <row r="179" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="45" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B179" s="46" t="s">
-        <v>505</v>
+        <v>562</v>
       </c>
       <c r="C179" s="47"/>
       <c r="D179" s="46" t="s">
-        <v>506</v>
+        <v>563</v>
       </c>
       <c r="E179" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9385,12 +10163,12 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B180" s="29"/>
       <c r="C180" s="30"/>
       <c r="D180" s="29" t="s">
-        <v>507</v>
+        <v>564</v>
       </c>
       <c r="E180" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9409,12 +10187,12 @@
     </row>
     <row r="181" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B181" s="29"/>
       <c r="C181" s="30"/>
       <c r="D181" s="29" t="s">
-        <v>508</v>
+        <v>565</v>
       </c>
       <c r="E181" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9433,12 +10211,12 @@
     </row>
     <row r="182" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B182" s="29"/>
       <c r="C182" s="30"/>
       <c r="D182" s="29" t="s">
-        <v>509</v>
+        <v>566</v>
       </c>
       <c r="E182" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9457,12 +10235,12 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B183" s="29"/>
       <c r="C183" s="30"/>
       <c r="D183" s="29" t="s">
-        <v>510</v>
+        <v>567</v>
       </c>
       <c r="E183" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9481,14 +10259,14 @@
     </row>
     <row r="184" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="45" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B184" s="46" t="s">
-        <v>512</v>
+        <v>569</v>
       </c>
       <c r="C184" s="47"/>
       <c r="D184" s="46" t="s">
-        <v>513</v>
+        <v>570</v>
       </c>
       <c r="E184" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9507,12 +10285,12 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B185" s="29"/>
       <c r="C185" s="30"/>
       <c r="D185" s="29" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
       <c r="E185" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9531,12 +10309,12 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B186" s="29"/>
       <c r="C186" s="30"/>
       <c r="D186" s="29" t="s">
-        <v>515</v>
+        <v>572</v>
       </c>
       <c r="E186" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9555,12 +10333,12 @@
     </row>
     <row r="187" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B187" s="29"/>
       <c r="C187" s="30"/>
       <c r="D187" s="29" t="s">
-        <v>516</v>
+        <v>573</v>
       </c>
       <c r="E187" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9579,12 +10357,12 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B188" s="29"/>
       <c r="C188" s="30"/>
       <c r="D188" s="29" t="s">
-        <v>517</v>
+        <v>574</v>
       </c>
       <c r="E188" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$25</f>
@@ -9603,14 +10381,14 @@
     </row>
     <row r="189" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="45" t="s">
-        <v>518</v>
+        <v>575</v>
       </c>
       <c r="B189" s="46" t="s">
-        <v>519</v>
+        <v>576</v>
       </c>
       <c r="C189" s="47"/>
       <c r="D189" s="46" t="s">
-        <v>520</v>
+        <v>577</v>
       </c>
       <c r="E189" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9629,12 +10407,12 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="31" t="s">
-        <v>518</v>
+        <v>575</v>
       </c>
       <c r="B190" s="29"/>
       <c r="C190" s="30"/>
       <c r="D190" s="29" t="s">
-        <v>521</v>
+        <v>578</v>
       </c>
       <c r="E190" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9653,12 +10431,12 @@
     </row>
     <row r="191" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="31" t="s">
-        <v>518</v>
+        <v>575</v>
       </c>
       <c r="B191" s="29"/>
       <c r="C191" s="30"/>
       <c r="D191" s="29" t="s">
-        <v>522</v>
+        <v>579</v>
       </c>
       <c r="E191" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9677,14 +10455,14 @@
     </row>
     <row r="192" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="45" t="s">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="B192" s="46" t="s">
-        <v>524</v>
+        <v>581</v>
       </c>
       <c r="C192" s="47"/>
       <c r="D192" s="46" t="s">
-        <v>525</v>
+        <v>582</v>
       </c>
       <c r="E192" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9703,12 +10481,12 @@
     </row>
     <row r="193" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="31" t="s">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="B193" s="29"/>
       <c r="C193" s="30"/>
       <c r="D193" s="29" t="s">
-        <v>526</v>
+        <v>583</v>
       </c>
       <c r="E193" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9727,12 +10505,12 @@
     </row>
     <row r="194" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="31" t="s">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="B194" s="29"/>
       <c r="C194" s="30"/>
       <c r="D194" s="29" t="s">
-        <v>527</v>
+        <v>584</v>
       </c>
       <c r="E194" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9751,16 +10529,16 @@
     </row>
     <row r="195" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="35" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B195" s="36" t="s">
-        <v>529</v>
+        <v>586</v>
       </c>
       <c r="C195" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D195" s="36" t="s">
-        <v>530</v>
+        <v>587</v>
       </c>
       <c r="E195" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9779,14 +10557,14 @@
     </row>
     <row r="196" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B196" s="43"/>
       <c r="C196" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D196" s="43" t="s">
-        <v>531</v>
+        <v>588</v>
       </c>
       <c r="E196" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9805,14 +10583,14 @@
     </row>
     <row r="197" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B197" s="43"/>
       <c r="C197" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D197" s="43" t="s">
-        <v>532</v>
+        <v>589</v>
       </c>
       <c r="E197" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9831,14 +10609,14 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B198" s="43"/>
       <c r="C198" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D198" s="43" t="s">
-        <v>533</v>
+        <v>590</v>
       </c>
       <c r="E198" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9857,14 +10635,14 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B199" s="43"/>
       <c r="C199" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D199" s="43" t="s">
-        <v>534</v>
+        <v>591</v>
       </c>
       <c r="E199" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9883,14 +10661,14 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B200" s="43"/>
       <c r="C200" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D200" s="43" t="s">
-        <v>535</v>
+        <v>592</v>
       </c>
       <c r="E200" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9909,14 +10687,14 @@
     </row>
     <row r="201" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="45" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B201" s="46" t="s">
-        <v>537</v>
+        <v>594</v>
       </c>
       <c r="C201" s="47"/>
       <c r="D201" s="46" t="s">
-        <v>538</v>
+        <v>595</v>
       </c>
       <c r="E201" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9935,12 +10713,12 @@
     </row>
     <row r="202" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B202" s="29"/>
       <c r="C202" s="30"/>
       <c r="D202" s="29" t="s">
-        <v>539</v>
+        <v>596</v>
       </c>
       <c r="E202" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9959,12 +10737,12 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B203" s="29"/>
       <c r="C203" s="30"/>
       <c r="D203" s="29" t="s">
-        <v>540</v>
+        <v>597</v>
       </c>
       <c r="E203" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -9983,12 +10761,12 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B204" s="29"/>
       <c r="C204" s="30"/>
       <c r="D204" s="29" t="s">
-        <v>541</v>
+        <v>598</v>
       </c>
       <c r="E204" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -10007,12 +10785,12 @@
     </row>
     <row r="205" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B205" s="29"/>
       <c r="C205" s="30"/>
       <c r="D205" s="29" t="s">
-        <v>542</v>
+        <v>599</v>
       </c>
       <c r="E205" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -10031,14 +10809,14 @@
     </row>
     <row r="206" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="45" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="B206" s="46" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="C206" s="47"/>
       <c r="D206" s="46" t="s">
-        <v>545</v>
+        <v>602</v>
       </c>
       <c r="E206" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -10057,12 +10835,12 @@
     </row>
     <row r="207" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="31" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="B207" s="29"/>
       <c r="C207" s="30"/>
       <c r="D207" s="29" t="s">
-        <v>546</v>
+        <v>603</v>
       </c>
       <c r="E207" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -10122,7 +10900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF8EA9DB"/>
@@ -10158,7 +10936,7 @@
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -10174,16 +10952,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>241</v>
+        <v>298</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>9</v>
@@ -10195,16 +10973,16 @@
         <v>89</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>245</v>
+        <v>302</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>247</v>
+        <v>304</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>99</v>
@@ -10212,14 +10990,14 @@
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>250</v>
+        <v>307</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="29" t="s">
-        <v>251</v>
+        <v>308</v>
       </c>
       <c r="E4" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10238,12 +11016,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="30"/>
       <c r="D5" s="29" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="E5" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10262,12 +11040,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B6" s="29"/>
       <c r="C6" s="30"/>
       <c r="D6" s="29" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="E6" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10286,12 +11064,12 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="29" t="s">
-        <v>254</v>
+        <v>311</v>
       </c>
       <c r="E7" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10310,16 +11088,16 @@
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>256</v>
+        <v>313</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>258</v>
+        <v>315</v>
       </c>
       <c r="E8" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10338,14 +11116,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="E9" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10364,14 +11142,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B10" s="43"/>
       <c r="C10" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="E10" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10390,14 +11168,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B11" s="43"/>
       <c r="C11" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="E11" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10416,14 +11194,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="42" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B12" s="43"/>
       <c r="C12" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>262</v>
+        <v>319</v>
       </c>
       <c r="E12" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10442,14 +11220,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="45" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="C13" s="47"/>
       <c r="D13" s="46" t="s">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="E13" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10468,12 +11246,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="29" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="E14" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10492,12 +11270,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="29" t="s">
-        <v>267</v>
+        <v>324</v>
       </c>
       <c r="E15" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10516,12 +11294,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="29" t="s">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="E16" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10540,12 +11318,12 @@
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="29" t="s">
-        <v>269</v>
+        <v>326</v>
       </c>
       <c r="E17" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10564,14 +11342,14 @@
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="C18" s="47"/>
       <c r="D18" s="46" t="s">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="E18" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10590,12 +11368,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="29" t="s">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="E19" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10614,14 +11392,14 @@
     </row>
     <row r="20" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="45" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>275</v>
+        <v>332</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="46" t="s">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="E20" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10640,12 +11418,12 @@
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="29" t="s">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="E21" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10664,12 +11442,12 @@
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="29" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="E22" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10688,12 +11466,12 @@
     </row>
     <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="29" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="E23" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10712,14 +11490,14 @@
     </row>
     <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="45" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>281</v>
+        <v>338</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="46" t="s">
-        <v>282</v>
+        <v>339</v>
       </c>
       <c r="E24" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10738,12 +11516,12 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="29" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="E25" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10762,12 +11540,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="29" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="E26" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10786,12 +11564,12 @@
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="29" t="s">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="E27" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10810,14 +11588,14 @@
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="45" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="C28" s="47"/>
       <c r="D28" s="46" t="s">
-        <v>288</v>
+        <v>345</v>
       </c>
       <c r="E28" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10836,12 +11614,12 @@
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="29" t="s">
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="E29" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10860,12 +11638,12 @@
     </row>
     <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="29" t="s">
-        <v>290</v>
+        <v>347</v>
       </c>
       <c r="E30" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10884,12 +11662,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="29" t="s">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="E31" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10908,12 +11686,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>286</v>
+        <v>343</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="29" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
       <c r="E32" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10932,16 +11710,16 @@
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="35" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>295</v>
+        <v>352</v>
       </c>
       <c r="E33" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10960,14 +11738,14 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B34" s="43"/>
       <c r="C34" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D34" s="43" t="s">
-        <v>296</v>
+        <v>353</v>
       </c>
       <c r="E34" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -10986,14 +11764,14 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B35" s="43"/>
       <c r="C35" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="E35" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11012,14 +11790,14 @@
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B36" s="43"/>
       <c r="C36" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="E36" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11038,14 +11816,14 @@
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B37" s="43"/>
       <c r="C37" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>299</v>
+        <v>356</v>
       </c>
       <c r="E37" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11064,14 +11842,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="42" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="B38" s="43"/>
       <c r="C38" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D38" s="43" t="s">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="E38" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11090,14 +11868,14 @@
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="45" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B39" s="46" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
       <c r="C39" s="47"/>
       <c r="D39" s="46" t="s">
-        <v>303</v>
+        <v>360</v>
       </c>
       <c r="E39" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11116,12 +11894,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="29" t="s">
-        <v>304</v>
+        <v>361</v>
       </c>
       <c r="E40" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11140,12 +11918,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="29" t="s">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="E41" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11164,12 +11942,12 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="29" t="s">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="E42" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11188,14 +11966,14 @@
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="45" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>308</v>
+        <v>365</v>
       </c>
       <c r="C43" s="47"/>
       <c r="D43" s="46" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
       <c r="E43" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11214,12 +11992,12 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="29" t="s">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="E44" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11238,12 +12016,12 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="31" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="29" t="s">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="E45" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11262,12 +12040,12 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="29" t="s">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="E46" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11286,16 +12064,16 @@
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="35" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="B47" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="C47" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="C47" s="37" t="s">
-        <v>257</v>
-      </c>
       <c r="D47" s="36" t="s">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="E47" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11314,14 +12092,14 @@
     </row>
     <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="42" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="B48" s="43"/>
       <c r="C48" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>316</v>
+        <v>373</v>
       </c>
       <c r="E48" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11340,14 +12118,14 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="42" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="B49" s="43"/>
       <c r="C49" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>317</v>
+        <v>374</v>
       </c>
       <c r="E49" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11366,14 +12144,14 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="45" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>319</v>
+        <v>376</v>
       </c>
       <c r="C50" s="47"/>
       <c r="D50" s="46" t="s">
-        <v>320</v>
+        <v>377</v>
       </c>
       <c r="E50" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11392,12 +12170,12 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="29" t="s">
-        <v>321</v>
+        <v>378</v>
       </c>
       <c r="E51" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11416,12 +12194,12 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="29" t="s">
-        <v>322</v>
+        <v>379</v>
       </c>
       <c r="E52" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11440,12 +12218,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="29" t="s">
-        <v>323</v>
+        <v>380</v>
       </c>
       <c r="E53" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11464,12 +12242,12 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="29" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="E54" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11488,12 +12266,12 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="31" t="s">
-        <v>318</v>
+        <v>375</v>
       </c>
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="29" t="s">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="E55" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$22</f>
@@ -11512,14 +12290,14 @@
     </row>
     <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="45" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B56" s="46" t="s">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="C56" s="47"/>
       <c r="D56" s="46" t="s">
-        <v>328</v>
+        <v>385</v>
       </c>
       <c r="E56" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11538,12 +12316,12 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="29" t="s">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="E57" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11562,12 +12340,12 @@
     </row>
     <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="29" t="s">
-        <v>330</v>
+        <v>387</v>
       </c>
       <c r="E58" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11586,12 +12364,12 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="29" t="s">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="E59" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11610,12 +12388,12 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="29" t="s">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="E60" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11634,12 +12412,12 @@
     </row>
     <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="29" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="E61" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11658,12 +12436,12 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="29" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="E62" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11682,12 +12460,12 @@
     </row>
     <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="29" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="E63" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11706,12 +12484,12 @@
     </row>
     <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="29" t="s">
-        <v>336</v>
+        <v>393</v>
       </c>
       <c r="E64" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11730,12 +12508,12 @@
     </row>
     <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="31" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="29" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="E65" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11754,16 +12532,16 @@
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="35" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="B66" s="36" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D66" s="36" t="s">
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="E66" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11782,14 +12560,14 @@
     </row>
     <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="42" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="B67" s="43"/>
       <c r="C67" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D67" s="43" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="E67" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11808,14 +12586,14 @@
     </row>
     <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="42" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="B68" s="43"/>
       <c r="C68" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D68" s="43" t="s">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="E68" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11834,14 +12612,14 @@
     </row>
     <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="45" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B69" s="46" t="s">
-        <v>344</v>
+        <v>401</v>
       </c>
       <c r="C69" s="47"/>
       <c r="D69" s="46" t="s">
-        <v>345</v>
+        <v>402</v>
       </c>
       <c r="E69" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11860,12 +12638,12 @@
     </row>
     <row r="70" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="31" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="29" t="s">
-        <v>346</v>
+        <v>403</v>
       </c>
       <c r="E70" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11884,12 +12662,12 @@
     </row>
     <row r="71" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="31" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="29" t="s">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="E71" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11908,12 +12686,12 @@
     </row>
     <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="31" t="s">
-        <v>343</v>
+        <v>400</v>
       </c>
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="29" t="s">
-        <v>348</v>
+        <v>405</v>
       </c>
       <c r="E72" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11932,16 +12710,16 @@
     </row>
     <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="35" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B73" s="36" t="s">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D73" s="36" t="s">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="E73" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11960,14 +12738,14 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="42" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B74" s="43"/>
       <c r="C74" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D74" s="43" t="s">
-        <v>351</v>
+        <v>408</v>
       </c>
       <c r="E74" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -11986,14 +12764,14 @@
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="42" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B75" s="43"/>
       <c r="C75" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D75" s="43" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="E75" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12012,14 +12790,14 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="42" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B76" s="43"/>
       <c r="C76" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D76" s="43" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="E76" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12038,14 +12816,14 @@
     </row>
     <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="45" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="C77" s="47"/>
       <c r="D77" s="46" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="E77" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12064,12 +12842,12 @@
     </row>
     <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="31" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="29" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="E78" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12088,12 +12866,12 @@
     </row>
     <row r="79" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="31" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="29" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
       <c r="E79" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12112,12 +12890,12 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="31" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="29" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="E80" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12136,16 +12914,16 @@
     </row>
     <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="35" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E81" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12164,14 +12942,14 @@
     </row>
     <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B82" s="43"/>
       <c r="C82" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D82" s="43" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="E82" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12190,14 +12968,14 @@
     </row>
     <row r="83" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B83" s="43"/>
       <c r="C83" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D83" s="43" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
       <c r="E83" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12216,14 +12994,14 @@
     </row>
     <row r="84" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B84" s="43"/>
       <c r="C84" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D84" s="43" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="E84" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12242,14 +13020,14 @@
     </row>
     <row r="85" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B85" s="43"/>
       <c r="C85" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D85" s="43" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="E85" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12268,14 +13046,14 @@
     </row>
     <row r="86" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="42" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="B86" s="43"/>
       <c r="C86" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D86" s="43" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="E86" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12294,16 +13072,16 @@
     </row>
     <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="35" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C87" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="E87" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12322,14 +13100,14 @@
     </row>
     <row r="88" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="42" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B88" s="43"/>
       <c r="C88" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="E88" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12348,14 +13126,14 @@
     </row>
     <row r="89" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="42" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B89" s="43"/>
       <c r="C89" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D89" s="43" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="E89" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12374,14 +13152,14 @@
     </row>
     <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="42" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="B90" s="43"/>
       <c r="C90" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D90" s="43" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="E90" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12400,14 +13178,14 @@
     </row>
     <row r="91" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="45" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B91" s="46" t="s">
-        <v>374</v>
+        <v>431</v>
       </c>
       <c r="C91" s="47"/>
       <c r="D91" s="46" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="E91" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12426,12 +13204,12 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="31" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B92" s="29"/>
       <c r="C92" s="30"/>
       <c r="D92" s="29" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="E92" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12450,12 +13228,12 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="31" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B93" s="29"/>
       <c r="C93" s="30"/>
       <c r="D93" s="29" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="E93" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12474,12 +13252,12 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="31" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="B94" s="29"/>
       <c r="C94" s="30"/>
       <c r="D94" s="29" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="E94" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12498,14 +13276,14 @@
     </row>
     <row r="95" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="45" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B95" s="46" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C95" s="47"/>
       <c r="D95" s="46" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="E95" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12524,12 +13302,12 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="31" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B96" s="29"/>
       <c r="C96" s="30"/>
       <c r="D96" s="29" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E96" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12548,12 +13326,12 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="31" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B97" s="29"/>
       <c r="C97" s="30"/>
       <c r="D97" s="29" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="E97" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12572,12 +13350,12 @@
     </row>
     <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="31" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="B98" s="29"/>
       <c r="C98" s="30"/>
       <c r="D98" s="29" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="E98" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12596,14 +13374,14 @@
     </row>
     <row r="99" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="45" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="B99" s="46" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="C99" s="47"/>
       <c r="D99" s="46" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="E99" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12622,12 +13400,12 @@
     </row>
     <row r="100" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="31" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="B100" s="29"/>
       <c r="C100" s="30"/>
       <c r="D100" s="29" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="E100" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12646,14 +13424,14 @@
     </row>
     <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="45" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B101" s="46" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="C101" s="47"/>
       <c r="D101" s="46" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="E101" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12672,12 +13450,12 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="31" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B102" s="29"/>
       <c r="C102" s="30"/>
       <c r="D102" s="29" t="s">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="E102" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12696,12 +13474,12 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="31" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="B103" s="29"/>
       <c r="C103" s="30"/>
       <c r="D103" s="29" t="s">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="E103" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12720,16 +13498,16 @@
     </row>
     <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="35" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>394</v>
+        <v>451</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D104" s="36" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
       <c r="E104" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12748,14 +13526,14 @@
     </row>
     <row r="105" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="42" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="B105" s="43"/>
       <c r="C105" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>396</v>
+        <v>453</v>
       </c>
       <c r="E105" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$24</f>
@@ -12774,16 +13552,16 @@
     </row>
     <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="35" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="C106" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>399</v>
+        <v>456</v>
       </c>
       <c r="E106" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12802,14 +13580,14 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B107" s="43"/>
       <c r="C107" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D107" s="43" t="s">
-        <v>400</v>
+        <v>457</v>
       </c>
       <c r="E107" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12828,14 +13606,14 @@
     </row>
     <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B108" s="43"/>
       <c r="C108" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D108" s="43" t="s">
-        <v>401</v>
+        <v>458</v>
       </c>
       <c r="E108" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12854,14 +13632,14 @@
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B109" s="43"/>
       <c r="C109" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="E109" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12880,14 +13658,14 @@
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="42" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="B110" s="43"/>
       <c r="C110" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D110" s="43" t="s">
-        <v>403</v>
+        <v>460</v>
       </c>
       <c r="E110" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12906,14 +13684,14 @@
     </row>
     <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="45" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B111" s="46" t="s">
-        <v>405</v>
+        <v>462</v>
       </c>
       <c r="C111" s="47"/>
       <c r="D111" s="46" t="s">
-        <v>406</v>
+        <v>463</v>
       </c>
       <c r="E111" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12932,12 +13710,12 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="31" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B112" s="29"/>
       <c r="C112" s="30"/>
       <c r="D112" s="29" t="s">
-        <v>407</v>
+        <v>464</v>
       </c>
       <c r="E112" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12956,12 +13734,12 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="31" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B113" s="29"/>
       <c r="C113" s="30"/>
       <c r="D113" s="29" t="s">
-        <v>408</v>
+        <v>465</v>
       </c>
       <c r="E113" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -12980,12 +13758,12 @@
     </row>
     <row r="114" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="31" t="s">
-        <v>404</v>
+        <v>461</v>
       </c>
       <c r="B114" s="29"/>
       <c r="C114" s="30"/>
       <c r="D114" s="29" t="s">
-        <v>409</v>
+        <v>466</v>
       </c>
       <c r="E114" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13004,14 +13782,14 @@
     </row>
     <row r="115" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="45" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="B115" s="46" t="s">
-        <v>411</v>
+        <v>468</v>
       </c>
       <c r="C115" s="47"/>
       <c r="D115" s="46" t="s">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="E115" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13030,12 +13808,12 @@
     </row>
     <row r="116" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="31" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="B116" s="29"/>
       <c r="C116" s="30"/>
       <c r="D116" s="29" t="s">
-        <v>413</v>
+        <v>470</v>
       </c>
       <c r="E116" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13054,12 +13832,12 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="31" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="B117" s="29"/>
       <c r="C117" s="30"/>
       <c r="D117" s="29" t="s">
-        <v>414</v>
+        <v>471</v>
       </c>
       <c r="E117" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13078,14 +13856,14 @@
     </row>
     <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="45" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="B118" s="46" t="s">
-        <v>416</v>
+        <v>473</v>
       </c>
       <c r="C118" s="47"/>
       <c r="D118" s="46" t="s">
-        <v>417</v>
+        <v>474</v>
       </c>
       <c r="E118" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13104,12 +13882,12 @@
     </row>
     <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="31" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="B119" s="29"/>
       <c r="C119" s="30"/>
       <c r="D119" s="29" t="s">
-        <v>418</v>
+        <v>475</v>
       </c>
       <c r="E119" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13128,12 +13906,12 @@
     </row>
     <row r="120" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="31" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="B120" s="29"/>
       <c r="C120" s="30"/>
       <c r="D120" s="29" t="s">
-        <v>419</v>
+        <v>476</v>
       </c>
       <c r="E120" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13152,14 +13930,14 @@
     </row>
     <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="45" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B121" s="46" t="s">
-        <v>421</v>
+        <v>478</v>
       </c>
       <c r="C121" s="47"/>
       <c r="D121" s="46" t="s">
-        <v>422</v>
+        <v>479</v>
       </c>
       <c r="E121" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13178,12 +13956,12 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B122" s="29"/>
       <c r="C122" s="30"/>
       <c r="D122" s="29" t="s">
-        <v>423</v>
+        <v>480</v>
       </c>
       <c r="E122" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13202,12 +13980,12 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B123" s="29"/>
       <c r="C123" s="30"/>
       <c r="D123" s="29" t="s">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="E123" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13226,12 +14004,12 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B124" s="29"/>
       <c r="C124" s="30"/>
       <c r="D124" s="29" t="s">
-        <v>425</v>
+        <v>482</v>
       </c>
       <c r="E124" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13250,12 +14028,12 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="31" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="B125" s="29"/>
       <c r="C125" s="30"/>
       <c r="D125" s="29" t="s">
-        <v>426</v>
+        <v>483</v>
       </c>
       <c r="E125" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13274,16 +14052,16 @@
     </row>
     <row r="126" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="35" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B126" s="36" t="s">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="C126" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D126" s="36" t="s">
-        <v>429</v>
+        <v>486</v>
       </c>
       <c r="E126" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13302,14 +14080,14 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B127" s="43"/>
       <c r="C127" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D127" s="43" t="s">
-        <v>430</v>
+        <v>487</v>
       </c>
       <c r="E127" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13328,14 +14106,14 @@
     </row>
     <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B128" s="43"/>
       <c r="C128" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D128" s="43" t="s">
-        <v>431</v>
+        <v>488</v>
       </c>
       <c r="E128" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13354,14 +14132,14 @@
     </row>
     <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B129" s="43"/>
       <c r="C129" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D129" s="43" t="s">
-        <v>432</v>
+        <v>489</v>
       </c>
       <c r="E129" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13380,14 +14158,14 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="42" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="B130" s="43"/>
       <c r="C130" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D130" s="43" t="s">
-        <v>433</v>
+        <v>490</v>
       </c>
       <c r="E130" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$19</f>
@@ -13406,14 +14184,14 @@
     </row>
     <row r="131" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="45" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B131" s="46" t="s">
-        <v>435</v>
+        <v>492</v>
       </c>
       <c r="C131" s="47"/>
       <c r="D131" s="46" t="s">
-        <v>436</v>
+        <v>493</v>
       </c>
       <c r="E131" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13432,12 +14210,12 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B132" s="29"/>
       <c r="C132" s="30"/>
       <c r="D132" s="29" t="s">
-        <v>437</v>
+        <v>494</v>
       </c>
       <c r="E132" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13456,12 +14234,12 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B133" s="29"/>
       <c r="C133" s="30"/>
       <c r="D133" s="29" t="s">
-        <v>438</v>
+        <v>495</v>
       </c>
       <c r="E133" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13480,12 +14258,12 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B134" s="29"/>
       <c r="C134" s="30"/>
       <c r="D134" s="29" t="s">
-        <v>439</v>
+        <v>496</v>
       </c>
       <c r="E134" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13504,12 +14282,12 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="31" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="B135" s="29"/>
       <c r="C135" s="30"/>
       <c r="D135" s="29" t="s">
-        <v>440</v>
+        <v>497</v>
       </c>
       <c r="E135" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13528,14 +14306,14 @@
     </row>
     <row r="136" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="45" t="s">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="B136" s="46" t="s">
-        <v>442</v>
+        <v>499</v>
       </c>
       <c r="C136" s="47"/>
       <c r="D136" s="46" t="s">
-        <v>443</v>
+        <v>500</v>
       </c>
       <c r="E136" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13554,12 +14332,12 @@
     </row>
     <row r="137" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="31" t="s">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="B137" s="29"/>
       <c r="C137" s="30"/>
       <c r="D137" s="29" t="s">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="E137" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13578,12 +14356,12 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="31" t="s">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="B138" s="29"/>
       <c r="C138" s="30"/>
       <c r="D138" s="29" t="s">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="E138" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13602,16 +14380,16 @@
     </row>
     <row r="139" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="35" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B139" s="36" t="s">
-        <v>447</v>
+        <v>504</v>
       </c>
       <c r="C139" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D139" s="36" t="s">
-        <v>448</v>
+        <v>505</v>
       </c>
       <c r="E139" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13630,14 +14408,14 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B140" s="43"/>
       <c r="C140" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D140" s="43" t="s">
-        <v>449</v>
+        <v>506</v>
       </c>
       <c r="E140" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13656,14 +14434,14 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B141" s="43"/>
       <c r="C141" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D141" s="43" t="s">
-        <v>450</v>
+        <v>507</v>
       </c>
       <c r="E141" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13682,14 +14460,14 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B142" s="43"/>
       <c r="C142" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D142" s="43" t="s">
-        <v>451</v>
+        <v>508</v>
       </c>
       <c r="E142" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13708,14 +14486,14 @@
     </row>
     <row r="143" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B143" s="43"/>
       <c r="C143" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D143" s="43" t="s">
-        <v>452</v>
+        <v>509</v>
       </c>
       <c r="E143" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13734,14 +14512,14 @@
     </row>
     <row r="144" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B144" s="43"/>
       <c r="C144" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D144" s="43" t="s">
-        <v>453</v>
+        <v>510</v>
       </c>
       <c r="E144" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13760,14 +14538,14 @@
     </row>
     <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="42" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B145" s="43"/>
       <c r="C145" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D145" s="43" t="s">
-        <v>454</v>
+        <v>511</v>
       </c>
       <c r="E145" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13786,14 +14564,14 @@
     </row>
     <row r="146" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="45" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B146" s="46" t="s">
-        <v>456</v>
+        <v>513</v>
       </c>
       <c r="C146" s="47"/>
       <c r="D146" s="46" t="s">
-        <v>457</v>
+        <v>514</v>
       </c>
       <c r="E146" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13812,12 +14590,12 @@
     </row>
     <row r="147" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="31" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B147" s="29"/>
       <c r="C147" s="30"/>
       <c r="D147" s="29" t="s">
-        <v>458</v>
+        <v>515</v>
       </c>
       <c r="E147" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13836,12 +14614,12 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="31" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B148" s="29"/>
       <c r="C148" s="30"/>
       <c r="D148" s="29" t="s">
-        <v>459</v>
+        <v>516</v>
       </c>
       <c r="E148" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13860,12 +14638,12 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="31" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="B149" s="29"/>
       <c r="C149" s="30"/>
       <c r="D149" s="29" t="s">
-        <v>460</v>
+        <v>517</v>
       </c>
       <c r="E149" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13884,14 +14662,14 @@
     </row>
     <row r="150" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="45" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B150" s="46" t="s">
-        <v>462</v>
+        <v>519</v>
       </c>
       <c r="C150" s="47"/>
       <c r="D150" s="46" t="s">
-        <v>463</v>
+        <v>520</v>
       </c>
       <c r="E150" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13910,12 +14688,12 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="31" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B151" s="29"/>
       <c r="C151" s="30"/>
       <c r="D151" s="29" t="s">
-        <v>464</v>
+        <v>521</v>
       </c>
       <c r="E151" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13934,12 +14712,12 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="31" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B152" s="29"/>
       <c r="C152" s="30"/>
       <c r="D152" s="29" t="s">
-        <v>465</v>
+        <v>522</v>
       </c>
       <c r="E152" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13958,12 +14736,12 @@
     </row>
     <row r="153" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="31" t="s">
-        <v>461</v>
+        <v>518</v>
       </c>
       <c r="B153" s="29"/>
       <c r="C153" s="30"/>
       <c r="D153" s="29" t="s">
-        <v>466</v>
+        <v>523</v>
       </c>
       <c r="E153" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -13982,14 +14760,14 @@
     </row>
     <row r="154" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="45" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B154" s="46" t="s">
-        <v>468</v>
+        <v>525</v>
       </c>
       <c r="C154" s="47"/>
       <c r="D154" s="46" t="s">
-        <v>469</v>
+        <v>526</v>
       </c>
       <c r="E154" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14008,12 +14786,12 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B155" s="29"/>
       <c r="C155" s="30"/>
       <c r="D155" s="29" t="s">
-        <v>470</v>
+        <v>527</v>
       </c>
       <c r="E155" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14032,12 +14810,12 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B156" s="29"/>
       <c r="C156" s="30"/>
       <c r="D156" s="29" t="s">
-        <v>471</v>
+        <v>528</v>
       </c>
       <c r="E156" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14056,12 +14834,12 @@
     </row>
     <row r="157" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B157" s="29"/>
       <c r="C157" s="30"/>
       <c r="D157" s="29" t="s">
-        <v>472</v>
+        <v>529</v>
       </c>
       <c r="E157" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14080,12 +14858,12 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B158" s="29"/>
       <c r="C158" s="30"/>
       <c r="D158" s="29" t="s">
-        <v>473</v>
+        <v>530</v>
       </c>
       <c r="E158" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14104,12 +14882,12 @@
     </row>
     <row r="159" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="31" t="s">
-        <v>467</v>
+        <v>524</v>
       </c>
       <c r="B159" s="29"/>
       <c r="C159" s="30"/>
       <c r="D159" s="29" t="s">
-        <v>474</v>
+        <v>531</v>
       </c>
       <c r="E159" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14128,16 +14906,16 @@
     </row>
     <row r="160" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="35" t="s">
-        <v>475</v>
+        <v>532</v>
       </c>
       <c r="B160" s="36" t="s">
-        <v>476</v>
+        <v>533</v>
       </c>
       <c r="C160" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D160" s="36" t="s">
-        <v>477</v>
+        <v>534</v>
       </c>
       <c r="E160" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14156,14 +14934,14 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="42" t="s">
-        <v>475</v>
+        <v>532</v>
       </c>
       <c r="B161" s="43"/>
       <c r="C161" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D161" s="43" t="s">
-        <v>478</v>
+        <v>535</v>
       </c>
       <c r="E161" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14182,14 +14960,14 @@
     </row>
     <row r="162" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="42" t="s">
-        <v>475</v>
+        <v>532</v>
       </c>
       <c r="B162" s="43"/>
       <c r="C162" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D162" s="43" t="s">
-        <v>479</v>
+        <v>536</v>
       </c>
       <c r="E162" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14208,16 +14986,16 @@
     </row>
     <row r="163" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="35" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B163" s="36" t="s">
-        <v>481</v>
+        <v>538</v>
       </c>
       <c r="C163" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D163" s="36" t="s">
-        <v>482</v>
+        <v>539</v>
       </c>
       <c r="E163" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14236,14 +15014,14 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="42" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B164" s="43"/>
       <c r="C164" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D164" s="43" t="s">
-        <v>483</v>
+        <v>540</v>
       </c>
       <c r="E164" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14262,14 +15040,14 @@
     </row>
     <row r="165" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="42" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B165" s="43"/>
       <c r="C165" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D165" s="43" t="s">
-        <v>484</v>
+        <v>541</v>
       </c>
       <c r="E165" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14288,14 +15066,14 @@
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="42" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B166" s="43"/>
       <c r="C166" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D166" s="43" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="E166" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14314,14 +15092,14 @@
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="45" t="s">
-        <v>486</v>
+        <v>543</v>
       </c>
       <c r="B167" s="46" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
       <c r="C167" s="47"/>
       <c r="D167" s="46" t="s">
-        <v>488</v>
+        <v>545</v>
       </c>
       <c r="E167" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14340,12 +15118,12 @@
     </row>
     <row r="168" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="31" t="s">
-        <v>486</v>
+        <v>543</v>
       </c>
       <c r="B168" s="29"/>
       <c r="C168" s="30"/>
       <c r="D168" s="29" t="s">
-        <v>489</v>
+        <v>546</v>
       </c>
       <c r="E168" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14364,14 +15142,14 @@
     </row>
     <row r="169" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="45" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B169" s="46" t="s">
-        <v>491</v>
+        <v>548</v>
       </c>
       <c r="C169" s="47"/>
       <c r="D169" s="46" t="s">
-        <v>492</v>
+        <v>549</v>
       </c>
       <c r="E169" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14390,12 +15168,12 @@
     </row>
     <row r="170" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B170" s="29"/>
       <c r="C170" s="30"/>
       <c r="D170" s="29" t="s">
-        <v>493</v>
+        <v>550</v>
       </c>
       <c r="E170" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14414,12 +15192,12 @@
     </row>
     <row r="171" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B171" s="29"/>
       <c r="C171" s="30"/>
       <c r="D171" s="29" t="s">
-        <v>494</v>
+        <v>551</v>
       </c>
       <c r="E171" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14438,12 +15216,12 @@
     </row>
     <row r="172" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B172" s="29"/>
       <c r="C172" s="30"/>
       <c r="D172" s="29" t="s">
-        <v>495</v>
+        <v>552</v>
       </c>
       <c r="E172" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14462,12 +15240,12 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B173" s="29"/>
       <c r="C173" s="30"/>
       <c r="D173" s="29" t="s">
-        <v>496</v>
+        <v>553</v>
       </c>
       <c r="E173" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14486,12 +15264,12 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B174" s="29"/>
       <c r="C174" s="30"/>
       <c r="D174" s="29" t="s">
-        <v>497</v>
+        <v>554</v>
       </c>
       <c r="E174" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14510,12 +15288,12 @@
     </row>
     <row r="175" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="31" t="s">
-        <v>490</v>
+        <v>547</v>
       </c>
       <c r="B175" s="29"/>
       <c r="C175" s="30"/>
       <c r="D175" s="29" t="s">
-        <v>498</v>
+        <v>555</v>
       </c>
       <c r="E175" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14534,14 +15312,14 @@
     </row>
     <row r="176" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="45" t="s">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="B176" s="46" t="s">
-        <v>500</v>
+        <v>557</v>
       </c>
       <c r="C176" s="47"/>
       <c r="D176" s="46" t="s">
-        <v>501</v>
+        <v>558</v>
       </c>
       <c r="E176" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14560,12 +15338,12 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="31" t="s">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="B177" s="29"/>
       <c r="C177" s="30"/>
       <c r="D177" s="29" t="s">
-        <v>502</v>
+        <v>559</v>
       </c>
       <c r="E177" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14584,12 +15362,12 @@
     </row>
     <row r="178" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="31" t="s">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="B178" s="29"/>
       <c r="C178" s="30"/>
       <c r="D178" s="29" t="s">
-        <v>503</v>
+        <v>560</v>
       </c>
       <c r="E178" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14608,14 +15386,14 @@
     </row>
     <row r="179" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="45" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B179" s="46" t="s">
-        <v>505</v>
+        <v>562</v>
       </c>
       <c r="C179" s="47"/>
       <c r="D179" s="46" t="s">
-        <v>506</v>
+        <v>563</v>
       </c>
       <c r="E179" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14634,12 +15412,12 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B180" s="29"/>
       <c r="C180" s="30"/>
       <c r="D180" s="29" t="s">
-        <v>507</v>
+        <v>564</v>
       </c>
       <c r="E180" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14658,12 +15436,12 @@
     </row>
     <row r="181" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B181" s="29"/>
       <c r="C181" s="30"/>
       <c r="D181" s="29" t="s">
-        <v>508</v>
+        <v>565</v>
       </c>
       <c r="E181" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14682,12 +15460,12 @@
     </row>
     <row r="182" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B182" s="29"/>
       <c r="C182" s="30"/>
       <c r="D182" s="29" t="s">
-        <v>509</v>
+        <v>566</v>
       </c>
       <c r="E182" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14706,12 +15484,12 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="31" t="s">
-        <v>504</v>
+        <v>561</v>
       </c>
       <c r="B183" s="29"/>
       <c r="C183" s="30"/>
       <c r="D183" s="29" t="s">
-        <v>510</v>
+        <v>567</v>
       </c>
       <c r="E183" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14730,14 +15508,14 @@
     </row>
     <row r="184" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="45" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B184" s="46" t="s">
-        <v>512</v>
+        <v>569</v>
       </c>
       <c r="C184" s="47"/>
       <c r="D184" s="46" t="s">
-        <v>513</v>
+        <v>570</v>
       </c>
       <c r="E184" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14756,12 +15534,12 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B185" s="29"/>
       <c r="C185" s="30"/>
       <c r="D185" s="29" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
       <c r="E185" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14780,12 +15558,12 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B186" s="29"/>
       <c r="C186" s="30"/>
       <c r="D186" s="29" t="s">
-        <v>515</v>
+        <v>572</v>
       </c>
       <c r="E186" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14804,12 +15582,12 @@
     </row>
     <row r="187" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B187" s="29"/>
       <c r="C187" s="30"/>
       <c r="D187" s="29" t="s">
-        <v>516</v>
+        <v>573</v>
       </c>
       <c r="E187" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14828,12 +15606,12 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="31" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="B188" s="29"/>
       <c r="C188" s="30"/>
       <c r="D188" s="29" t="s">
-        <v>517</v>
+        <v>574</v>
       </c>
       <c r="E188" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$26</f>
@@ -14852,14 +15630,14 @@
     </row>
     <row r="189" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="45" t="s">
-        <v>518</v>
+        <v>575</v>
       </c>
       <c r="B189" s="46" t="s">
-        <v>519</v>
+        <v>576</v>
       </c>
       <c r="C189" s="47"/>
       <c r="D189" s="46" t="s">
-        <v>520</v>
+        <v>577</v>
       </c>
       <c r="E189" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -14878,12 +15656,12 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="31" t="s">
-        <v>518</v>
+        <v>575</v>
       </c>
       <c r="B190" s="29"/>
       <c r="C190" s="30"/>
       <c r="D190" s="29" t="s">
-        <v>521</v>
+        <v>578</v>
       </c>
       <c r="E190" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -14902,12 +15680,12 @@
     </row>
     <row r="191" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="31" t="s">
-        <v>518</v>
+        <v>575</v>
       </c>
       <c r="B191" s="29"/>
       <c r="C191" s="30"/>
       <c r="D191" s="29" t="s">
-        <v>522</v>
+        <v>579</v>
       </c>
       <c r="E191" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -14926,14 +15704,14 @@
     </row>
     <row r="192" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="45" t="s">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="B192" s="46" t="s">
-        <v>524</v>
+        <v>581</v>
       </c>
       <c r="C192" s="47"/>
       <c r="D192" s="46" t="s">
-        <v>525</v>
+        <v>582</v>
       </c>
       <c r="E192" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -14952,12 +15730,12 @@
     </row>
     <row r="193" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="31" t="s">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="B193" s="29"/>
       <c r="C193" s="30"/>
       <c r="D193" s="29" t="s">
-        <v>526</v>
+        <v>583</v>
       </c>
       <c r="E193" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -14976,12 +15754,12 @@
     </row>
     <row r="194" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="31" t="s">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="B194" s="29"/>
       <c r="C194" s="30"/>
       <c r="D194" s="29" t="s">
-        <v>527</v>
+        <v>584</v>
       </c>
       <c r="E194" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15000,16 +15778,16 @@
     </row>
     <row r="195" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="35" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B195" s="36" t="s">
-        <v>529</v>
+        <v>586</v>
       </c>
       <c r="C195" s="37" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D195" s="36" t="s">
-        <v>530</v>
+        <v>587</v>
       </c>
       <c r="E195" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15028,14 +15806,14 @@
     </row>
     <row r="196" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B196" s="43"/>
       <c r="C196" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D196" s="43" t="s">
-        <v>531</v>
+        <v>588</v>
       </c>
       <c r="E196" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15054,14 +15832,14 @@
     </row>
     <row r="197" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B197" s="43"/>
       <c r="C197" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D197" s="43" t="s">
-        <v>532</v>
+        <v>589</v>
       </c>
       <c r="E197" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15080,14 +15858,14 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B198" s="43"/>
       <c r="C198" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D198" s="43" t="s">
-        <v>533</v>
+        <v>590</v>
       </c>
       <c r="E198" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15106,14 +15884,14 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B199" s="43"/>
       <c r="C199" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D199" s="43" t="s">
-        <v>534</v>
+        <v>591</v>
       </c>
       <c r="E199" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15132,14 +15910,14 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="42" t="s">
-        <v>528</v>
+        <v>585</v>
       </c>
       <c r="B200" s="43"/>
       <c r="C200" s="44" t="s">
-        <v>257</v>
+        <v>314</v>
       </c>
       <c r="D200" s="43" t="s">
-        <v>535</v>
+        <v>592</v>
       </c>
       <c r="E200" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15158,14 +15936,14 @@
     </row>
     <row r="201" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="45" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B201" s="46" t="s">
-        <v>537</v>
+        <v>594</v>
       </c>
       <c r="C201" s="47"/>
       <c r="D201" s="46" t="s">
-        <v>538</v>
+        <v>595</v>
       </c>
       <c r="E201" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15184,12 +15962,12 @@
     </row>
     <row r="202" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B202" s="29"/>
       <c r="C202" s="30"/>
       <c r="D202" s="29" t="s">
-        <v>539</v>
+        <v>596</v>
       </c>
       <c r="E202" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15208,12 +15986,12 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B203" s="29"/>
       <c r="C203" s="30"/>
       <c r="D203" s="29" t="s">
-        <v>540</v>
+        <v>597</v>
       </c>
       <c r="E203" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15232,12 +16010,12 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B204" s="29"/>
       <c r="C204" s="30"/>
       <c r="D204" s="29" t="s">
-        <v>541</v>
+        <v>598</v>
       </c>
       <c r="E204" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15256,12 +16034,12 @@
     </row>
     <row r="205" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="31" t="s">
-        <v>536</v>
+        <v>593</v>
       </c>
       <c r="B205" s="29"/>
       <c r="C205" s="30"/>
       <c r="D205" s="29" t="s">
-        <v>542</v>
+        <v>599</v>
       </c>
       <c r="E205" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15280,14 +16058,14 @@
     </row>
     <row r="206" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="45" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="B206" s="46" t="s">
-        <v>544</v>
+        <v>601</v>
       </c>
       <c r="C206" s="47"/>
       <c r="D206" s="46" t="s">
-        <v>545</v>
+        <v>602</v>
       </c>
       <c r="E206" s="38" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
@@ -15306,12 +16084,12 @@
     </row>
     <row r="207" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="31" t="s">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="B207" s="29"/>
       <c r="C207" s="30"/>
       <c r="D207" s="29" t="s">
-        <v>546</v>
+        <v>603</v>
       </c>
       <c r="E207" s="31" t="str">
         <f aca="false">'الخطة واللجنة'!$B$20</f>
